--- a/docs/sprint3/test-cases.xlsx
+++ b/docs/sprint3/test-cases.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Шапка містить назву готелю ліворуч і сім посилань меню праворуч</t>
+          <t>Шапка містить назву готелю ліворуч і шість посилань меню праворуч</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-70, GUI-85</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Сторінка відкрита.
-2. Форму видно.
+2. Форму видно: поля «Name», «Email», «Phone», «Subject», багаторядкове поле «Message» і кнопка «Submit».
 3. Поля містять уведені значення.
 4. Форма замінюється текстом «Thanks for getting in touch Olena Testova!» з темою «Rooms».</t>
         </is>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1933,14 +1933,14 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Браузер відкрито, користувач не автентифікований. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Браузер відкрито, користувач не автентифікований. Chrome 131, Windows 11, нова сесія (вікно інкогніто); форму «Send Us a Message» у цій сесії не надсилали</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити https://automationintesting.online у Chrome.
 2. Прокрутити до форми «Send Us a Message».
-3. Увести Name «Olena Testova», Email «olena.testova@example.com», Phone «06712345678», Subject із рівно 100 символів (рядок «Booking question about availability of the single room for the November dates and breakfast tim»), Message «Twenty chars message».
+3. Увести Name «Olena Testova», Email «olena.testova@example.com», Phone «06712345678», Subject із рівно 100 символів (рядок «Booking question about availability of the single room for the November dates and the breakfast time»), Message «Twenty chars message».
 4. Натиснути «Submit».</t>
         </is>
       </c>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
         <is>
           <t>1. Відкрити https://automationintesting.online у Chrome.
 2. Прокрутити до форми «Send Us a Message».
-3. Увести Name «Olena Testova», Email «olena.testova@example.com», Phone «06712345678», Subject із рівно 101 символу, Message «Twenty chars message».
+3. Увести Name «Olena Testova», Email «olena.testova@example.com», Phone «06712345678», Subject із рівно 101 символу (рядок «Booking question about availability of the single room for the November dates and the breakfast times» — рядок TC-022 плюс один символ), Message «Twenty chars message».
 4. Натиснути «Submit».</t>
         </is>
       </c>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
         <is>
           <t>1. Відкрити https://automationintesting.online у Chrome.
 2. Прокрутити до форми «Send Us a Message».
-3. Увести Name «Olena Testova», Email «olena.testova@example.com», Phone «06712345678», Subject «Rooms», Message «Short message 19ch» (19 символів).
+3. Увести Name «Olena Testova», Email «olena.testova@example.com», Phone «06712345678», Subject «Rooms», Message «Short message 19chr» (19 символів).
 4. Натиснути «Submit».</t>
         </is>
       </c>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GUI-85</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
         <is>
           <t>1. Сторінка відкрита.
 2. Форму видно.
-3. Показано перелік помилок валідації.
+3. Показано перелік помилок валідації, серед них дослівно «Name may not be blank», «Subject may not be blank», «Message may not be blank».
 4. Блок з помилками розташований над кнопкою «Submit».</t>
         </is>
       </c>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>F-80</t>
+          <t>GUI-70</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Вхід із неправильним паролем не надає доступу до адмінпанелі</t>
+          <t>Вхід із неправильним паролем: поля форми позначаються як помилкові і доступу немає</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password; номер 9901 у переліку номерів відсутній</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Браузер відкрито, користувач не автентифікований. Chrome 131, Windows 11, нова сесія (вікно інкогніто); обліковий запис адміністратора admin / password</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Виконано вхід до адмінпанелі обліковим записом admin / password. Chrome 131, Windows 11, нова сесія (вікно інкогніто)</t>
+          <t>Chrome 131, Windows 11, окреме вікно інкогніто; безпосередньо перед кейсом виконано вхід до адмінпанелі обліковим записом admin / password</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>кейси заблоковані дефектом BUG-001 (сторінка номера не відкривається)</t>
+          <t>Покрито: кейс виконано, виявлено дефект BUG-001 (сторінка номера не відкривається) — статус failed</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>кейси заблоковані дефектом BUG-001 (сторінка номера не відкривається)</t>
+          <t>Кейси TC-015 і TC-017 заблоковані дефектом BUG-001: сторінка номера не відкривається</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TC-018, TC-019, TC-020, TC-021, TC-022, TC-023, TC-024, TC-025, TC-026, TC-027, TC-028, TC-029, TC-030</t>
+          <t>TC-018, TC-019, TC-020, TC-021, TC-022, TC-023, TC-024, TC-025, TC-026, TC-027, TC-028, TC-029, TC-030, TC-031</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TC-033, TC-034, TC-035</t>
+          <t>TC-033, TC-035</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>кейси заблоковані дефектом BUG-001 (сторінка номера не відкривається)</t>
+          <t>Кейс TC-014 заблокований дефектом BUG-001</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>кейси заблоковані дефектом BUG-001 (сторінка номера не відкривається)</t>
+          <t>Кейс TC-013 заблокований дефектом BUG-001</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TC-036</t>
+          <t>TC-034, TC-036</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>кейси заблоковані дефектом BUG-001 (сторінка номера не відкривається)</t>
+          <t>Кейс TC-016 заблокований дефектом BUG-001</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>TC-031</t>
+          <t>TC-018</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Не покрито повністю: наявний кейс TC-012 перевіряє лише час відповіді переліку номерів; емуляція 4G не виконувалась</t>
+          <t>Не покрито повністю: наявний кейс TC-008 перевіряє лише час відповіді переліку номерів; емуляція 4G не виконувалась</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4455,17 +4455,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Зауважень немає</t>
+          <t>Узгодити заголовок із переліком посилань у вимозі GUI-10: шість, не сім</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Розділити перевірку дат і перевірку переліку номерів на два очікувані результати</t>
+          <t>Розкласти «Price Summary» в очікуваному результаті на окремі значення: ночі, Cleaning fee, Service fee і Total</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4887,17 +4887,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Зауважень немає</t>
+          <t>Додати до результату склад форми: кейс покриває і GUI-85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Додати у передумови стан «форму не надсилали в цій сесії»</t>
+          <t>Додати у передумови стан «форму не надсилали в цій сесії» і навести рядок теми зі 100 символів дослівно</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Зауважень немає</t>
+          <t>Навести рядок теми зі 101 символу дослівно</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Зауважень немає</t>
+          <t>Привести текст повідомлення до рівно 19 символів</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Вказати точну довжину теми в символах у кроці 3</t>
+          <t>Вказати точну довжину телефону в символах у кроці 3</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Додати у результат текст повідомлення про помилку дослівно</t>
+          <t>Додати у результат текст повідомлень про помилку дослівно; вимога — F-70 (розташування переліку помилок), не GUI-85</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5319,17 +5319,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Зауважень немає</t>
+          <t>Вимога — GUI-70: позначення полів як помилкових описане саме в ній, не у F-80</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Уточнити, що пароль вводиться у вікні інкогніто</t>
+          <t>Додати до очікуваного результату стан після виходу: адреса /admin і форма «Login»</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Додати крок із перевіркою адреси після виходу</t>
+          <t>Вказати у передумовах, що номер 9901 ще не створений</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Вказати у передумовах, що номер 9901 ще не створений</t>
+          <t>Навести у кроці 1 дані надісланого повідомлення (Name, Subject), щоб кейс не залежав від чужих даних</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Додати очікуваний текст повідомлення про незаповнені поля</t>
+          <t>Перелічити в очікуваному результаті елементи звіту: назву місяця, рік і кнопки «Today», «Back», «Next»</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
